--- a/input/계약정보/▶ thynC 계약서 현황관리_영업관리1팀 260625~.xlsx
+++ b/input/계약정보/▶ thynC 계약서 현황관리_영업관리1팀 260625~.xlsx
@@ -5033,7 +5033,7 @@
         <v>18</v>
       </c>
       <c r="G27" s="108" t="n">
-        <v>143533000</v>
+        <v>489469500</v>
       </c>
       <c r="H27" s="22" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>259</v>
       </c>
       <c r="G73" s="108" t="n">
-        <v>1521496500</v>
+        <v>98145000</v>
       </c>
       <c r="H73" s="22" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>100</v>
       </c>
       <c r="G77" s="108" t="n">
-        <v>571548000</v>
+        <v>532358000</v>
       </c>
       <c r="H77" s="22" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>70</v>
       </c>
       <c r="G92" s="108" t="n">
-        <v>467995000</v>
+        <v>417891900</v>
       </c>
       <c r="H92" s="22" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>120</v>
       </c>
       <c r="G139" s="108" t="n">
-        <v>855722400</v>
+        <v>837272000</v>
       </c>
       <c r="H139" s="22" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>100</v>
       </c>
       <c r="G187" s="108" t="n">
-        <v>572948000</v>
+        <v>532358000</v>
       </c>
       <c r="H187" s="22" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>156</v>
       </c>
       <c r="G189" s="108" t="n">
-        <v>974066000</v>
+        <v>2054066000</v>
       </c>
       <c r="H189" s="22" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>110</v>
       </c>
       <c r="G191" s="108" t="n">
-        <v>972272340</v>
+        <v>983759140</v>
       </c>
       <c r="H191" s="22" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>50</v>
       </c>
       <c r="G239" s="108" t="n">
-        <v>417890900</v>
+        <v>417891900</v>
       </c>
       <c r="H239" s="22" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>50</v>
       </c>
       <c r="G247" s="108" t="n">
-        <v>326548000</v>
+        <v>436766000</v>
       </c>
       <c r="H247" s="22" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>150</v>
       </c>
       <c r="G254" s="108" t="n">
-        <v>1392110000</v>
+        <v>1621240000</v>
       </c>
       <c r="H254" s="22" t="n"/>
       <c r="I254" s="23" t="n"/>
@@ -16355,7 +16355,7 @@
         <v>40</v>
       </c>
       <c r="G258" s="108" t="n">
-        <v>452650075</v>
+        <v>249237000</v>
       </c>
       <c r="H258" s="22" t="inlineStr">
         <is>

--- a/input/계약정보/▶ thynC 계약서 현황관리_영업관리1팀 260625~.xlsx
+++ b/input/계약정보/▶ thynC 계약서 현황관리_영업관리1팀 260625~.xlsx
@@ -4203,7 +4203,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="108" t="n">
-        <v>291461099</v>
+        <v>114172800</v>
       </c>
       <c r="H8" s="22" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>40</v>
       </c>
       <c r="G15" s="108" t="n">
-        <v>198000000</v>
+        <v>654321000</v>
       </c>
       <c r="H15" s="22" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>10</v>
       </c>
       <c r="G19" s="108" t="n">
-        <v>299145829</v>
+        <v>100053000</v>
       </c>
       <c r="H19" s="22" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>10</v>
       </c>
       <c r="G23" s="108" t="n">
-        <v>505204000</v>
+        <v>125000000</v>
       </c>
       <c r="H23" s="22" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>18</v>
       </c>
       <c r="G27" s="108" t="n">
-        <v>489469500</v>
+        <v>143533000</v>
       </c>
       <c r="H27" s="22" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>30</v>
       </c>
       <c r="G30" s="108" t="n">
-        <v>195000000</v>
+        <v>24920000</v>
       </c>
       <c r="H30" s="22" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="F31" s="109" t="n"/>
       <c r="G31" s="108" t="n">
-        <v>1250330000</v>
+        <v>203000000</v>
       </c>
       <c r="H31" s="22" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>30</v>
       </c>
       <c r="G42" s="108" t="n">
-        <v>346947000</v>
+        <v>351426000</v>
       </c>
       <c r="H42" s="22" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>20</v>
       </c>
       <c r="G47" s="108" t="n">
-        <v>120141000</v>
+        <v>145151000</v>
       </c>
       <c r="H47" s="22" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>259</v>
       </c>
       <c r="G73" s="108" t="n">
-        <v>98145000</v>
+        <v>1521496500</v>
       </c>
       <c r="H73" s="22" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>48</v>
       </c>
       <c r="G74" s="108" t="n">
-        <v>291049000</v>
+        <v>632326000</v>
       </c>
       <c r="H74" s="22" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>100</v>
       </c>
       <c r="G77" s="108" t="n">
-        <v>532358000</v>
+        <v>571548000</v>
       </c>
       <c r="H77" s="22" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>70</v>
       </c>
       <c r="G92" s="108" t="n">
-        <v>417891900</v>
+        <v>467995000</v>
       </c>
       <c r="H92" s="22" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>100</v>
       </c>
       <c r="G107" s="108" t="n">
-        <v>659977000</v>
+        <v>476620000</v>
       </c>
       <c r="H107" s="22" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>40</v>
       </c>
       <c r="G121" s="108" t="n">
-        <v>219832000</v>
+        <v>477867000</v>
       </c>
       <c r="H121" s="22" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>30</v>
       </c>
       <c r="G127" s="108" t="n">
-        <v>276460470</v>
+        <v>338927437</v>
       </c>
       <c r="H127" s="22" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>555</v>
       </c>
       <c r="G152" s="108" t="n">
-        <v>4753919201</v>
+        <v>2445025466</v>
       </c>
       <c r="H152" s="22" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>49</v>
       </c>
       <c r="G161" s="108" t="n">
-        <v>282030000</v>
+        <v>98145000</v>
       </c>
       <c r="H161" s="22" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>125</v>
       </c>
       <c r="G183" s="108" t="n">
-        <v>1087076900</v>
+        <v>1553158100</v>
       </c>
       <c r="H183" s="22" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>100</v>
       </c>
       <c r="G187" s="108" t="n">
-        <v>532358000</v>
+        <v>572948000</v>
       </c>
       <c r="H187" s="22" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>156</v>
       </c>
       <c r="G189" s="108" t="n">
-        <v>2054066000</v>
+        <v>974066000</v>
       </c>
       <c r="H189" s="22" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>110</v>
       </c>
       <c r="G191" s="108" t="n">
-        <v>983759140</v>
+        <v>972272340</v>
       </c>
       <c r="H191" s="22" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>60</v>
       </c>
       <c r="G206" s="108" t="n">
-        <v>408776000</v>
+        <v>380616000</v>
       </c>
       <c r="H206" s="22" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>191</v>
       </c>
       <c r="G221" s="108" t="n">
-        <v>1114876000</v>
+        <v>1171729000</v>
       </c>
       <c r="H221" s="22" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>50</v>
       </c>
       <c r="G239" s="108" t="n">
-        <v>417891900</v>
+        <v>417890900</v>
       </c>
       <c r="H239" s="22" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>10</v>
       </c>
       <c r="G259" s="108" t="n">
-        <v>48787200</v>
+        <v>435158557</v>
       </c>
       <c r="H259" s="22" t="inlineStr">
         <is>

--- a/input/계약정보/▶ thynC 계약서 현황관리_영업관리1팀 260625~.xlsx
+++ b/input/계약정보/▶ thynC 계약서 현황관리_영업관리1팀 260625~.xlsx
@@ -4203,7 +4203,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="108" t="n">
-        <v>114172800</v>
+        <v>291461099</v>
       </c>
       <c r="H8" s="22" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>12</v>
       </c>
       <c r="G14" s="108" t="n">
-        <v>112436100</v>
+        <v>489469500</v>
       </c>
       <c r="H14" s="22" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>20</v>
       </c>
       <c r="G16" s="108" t="n">
-        <v>139367500</v>
+        <v>786702070</v>
       </c>
       <c r="H16" s="22" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>10</v>
       </c>
       <c r="G19" s="108" t="n">
-        <v>100053000</v>
+        <v>299145829</v>
       </c>
       <c r="H19" s="22" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>54</v>
       </c>
       <c r="G22" s="108" t="n">
-        <v>310938000</v>
+        <v>477867000</v>
       </c>
       <c r="H22" s="22" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>10</v>
       </c>
       <c r="G23" s="108" t="n">
-        <v>125000000</v>
+        <v>505204000</v>
       </c>
       <c r="H23" s="22" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>18</v>
       </c>
       <c r="G27" s="108" t="n">
-        <v>143533000</v>
+        <v>489469500</v>
       </c>
       <c r="H27" s="22" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="F31" s="109" t="n"/>
       <c r="G31" s="108" t="n">
-        <v>203000000</v>
+        <v>1250330000</v>
       </c>
       <c r="H31" s="22" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>40</v>
       </c>
       <c r="G34" s="108" t="n">
-        <v>414938000</v>
+        <v>505204000</v>
       </c>
       <c r="H34" s="22" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>20</v>
       </c>
       <c r="G35" s="108" t="n">
-        <v>139367500</v>
+        <v>786702070</v>
       </c>
       <c r="H35" s="22" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>20</v>
       </c>
       <c r="G47" s="108" t="n">
-        <v>145151000</v>
+        <v>120141000</v>
       </c>
       <c r="H47" s="22" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>26</v>
       </c>
       <c r="G65" s="108" t="n">
-        <v>166920000</v>
+        <v>477867000</v>
       </c>
       <c r="H65" s="22" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>259</v>
       </c>
       <c r="G73" s="108" t="n">
-        <v>1521496500</v>
+        <v>98145000</v>
       </c>
       <c r="H73" s="22" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>241</v>
       </c>
       <c r="G98" s="108" t="n">
-        <v>1192270000</v>
+        <v>390773875</v>
       </c>
       <c r="H98" s="22" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>30</v>
       </c>
       <c r="G127" s="108" t="n">
-        <v>338927437</v>
+        <v>276460470</v>
       </c>
       <c r="H127" s="22" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>98</v>
       </c>
       <c r="G171" s="108" t="n">
-        <v>477847000</v>
+        <v>287374000</v>
       </c>
       <c r="H171" s="22" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>228</v>
       </c>
       <c r="G174" s="108" t="n">
-        <v>1146845000</v>
+        <v>390773875</v>
       </c>
       <c r="H174" s="22" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>120</v>
       </c>
       <c r="G178" s="108" t="n">
-        <v>865049000</v>
+        <v>994806350</v>
       </c>
       <c r="H178" s="22" t="inlineStr">
         <is>
